--- a/metas.xlsx
+++ b/metas.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="280">
   <si>
     <t>Distribuidor:</t>
   </si>
@@ -377,9 +377,6 @@
     <t>TELEMARKETING</t>
   </si>
   <si>
-    <t>JOSE VENTURA ROJAS</t>
-  </si>
-  <si>
     <t>Sucursal TR</t>
   </si>
   <si>
@@ -389,9 +386,6 @@
     <t>&lt; 75%</t>
   </si>
   <si>
-    <t>MANUEL BOTELLO P.</t>
-  </si>
-  <si>
     <t>sucursal GP</t>
   </si>
   <si>
@@ -456,9 +450,6 @@
   </si>
   <si>
     <t>HUGO ALBERTO BERNAL CASTILLO</t>
-  </si>
-  <si>
-    <t>Alfredo Pizaña Samaniego</t>
   </si>
   <si>
     <t>120% &lt; 133%</t>
@@ -2799,7 +2790,7 @@
         <v>103</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>106</v>
+        <v>172</v>
       </c>
       <c r="D2" s="74">
         <v>1000000</v>
@@ -2841,13 +2832,13 @@
         <v>115</v>
       </c>
       <c r="C3" s="41" t="s">
-        <v>116</v>
+        <v>187</v>
       </c>
       <c r="D3" s="74">
         <v>950000</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G3" s="76">
         <v>5000000</v>
@@ -2855,10 +2846,10 @@
       <c r="H3" s="79"/>
       <c r="I3" s="84"/>
       <c r="J3" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="K3" s="47" t="s">
         <v>118</v>
-      </c>
-      <c r="K3" s="47" t="s">
-        <v>119</v>
       </c>
       <c r="L3" s="48">
         <v>0</v>
@@ -2881,13 +2872,13 @@
         <v>104</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>120</v>
+        <v>279</v>
       </c>
       <c r="D4" s="74">
         <v>900000</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G4" s="76">
         <v>7000000</v>
@@ -2895,10 +2886,10 @@
       <c r="H4" s="79"/>
       <c r="I4" s="84"/>
       <c r="J4" s="51" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K4" s="52" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L4" s="48">
         <v>0.75</v>
@@ -2925,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G5" s="76">
         <v>2100000</v>
@@ -2933,10 +2924,10 @@
       <c r="H5" s="79"/>
       <c r="I5" s="84"/>
       <c r="J5" s="54" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K5" s="52" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L5" s="48">
         <v>1.1000000000000001</v>
@@ -2959,13 +2950,13 @@
         <v>104</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="D6" s="74">
         <v>900000</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G6" s="74">
         <v>2100000</v>
@@ -2973,16 +2964,16 @@
       <c r="H6" s="80"/>
       <c r="I6" s="84"/>
       <c r="J6" s="56" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K6" s="52" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L6" s="48">
         <v>1.2</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="O6" s="57">
         <v>1.7500000000000002E-2</v>
@@ -2999,13 +2990,13 @@
         <v>103</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D7" s="74">
         <v>1000000</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G7" s="77">
         <v>16200000</v>
@@ -3014,7 +3005,7 @@
     </row>
     <row r="8" spans="1:16" ht="26.4" customHeight="1">
       <c r="A8" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>103</v>
@@ -3024,43 +3015,43 @@
         <v>0</v>
       </c>
       <c r="I8" s="83" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J8" s="61" t="s">
         <v>109</v>
       </c>
       <c r="K8" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="L8" s="65" t="s">
+        <v>135</v>
+      </c>
+      <c r="M8" s="65" t="s">
         <v>136</v>
       </c>
-      <c r="L8" s="65" t="s">
+      <c r="O8" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="M8" s="65" t="s">
+      <c r="P8" s="63" t="s">
         <v>138</v>
-      </c>
-      <c r="O8" s="63" t="s">
-        <v>139</v>
-      </c>
-      <c r="P8" s="63" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="14.4" customHeight="1">
       <c r="A9" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B9" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D9" s="74">
         <v>2000000</v>
       </c>
       <c r="I9" s="84"/>
       <c r="J9" s="46" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K9" s="47">
         <v>0</v>
@@ -3080,23 +3071,23 @@
     </row>
     <row r="10" spans="1:16" ht="14.4" customHeight="1">
       <c r="A10" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B10" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D10" s="74">
         <v>950000</v>
       </c>
       <c r="I10" s="84"/>
       <c r="J10" s="51" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L10" s="48">
         <v>1.1000000000000001</v>
@@ -3113,23 +3104,23 @@
     </row>
     <row r="11" spans="1:16" ht="14.4" customHeight="1">
       <c r="A11" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B11" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="D11" s="74">
         <v>1000000</v>
       </c>
       <c r="I11" s="84"/>
       <c r="J11" s="54" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L11" s="48">
         <v>1.2</v>
@@ -3146,21 +3137,21 @@
     </row>
     <row r="12" spans="1:16" ht="14.4" customHeight="1">
       <c r="A12" s="40" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D12" s="74"/>
       <c r="I12" s="84"/>
       <c r="J12" s="56" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L12" s="48">
         <v>1.3333333999999999</v>
@@ -3177,22 +3168,22 @@
     </row>
     <row r="13" spans="1:16" ht="14.4" customHeight="1">
       <c r="A13" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D13" s="74">
         <v>1000000</v>
       </c>
       <c r="J13" s="58" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="L13" s="48">
         <v>1.5</v>
@@ -3203,22 +3194,22 @@
     </row>
     <row r="14" spans="1:16" ht="14.4" customHeight="1">
       <c r="A14" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="D14" s="74">
         <v>2200000</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L14" s="48">
         <v>1.6</v>
@@ -3229,13 +3220,13 @@
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" thickBot="1">
       <c r="A15" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B15" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D15" s="74">
         <v>1050000</v>
@@ -3249,36 +3240,36 @@
     </row>
     <row r="16" spans="1:16" ht="43.2" customHeight="1" thickBot="1">
       <c r="A16" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B16" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D16" s="74">
         <v>1050000</v>
       </c>
       <c r="M16" s="85" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="O16" s="63" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="P16" s="63" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="14.4" customHeight="1">
       <c r="A17" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D17" s="74"/>
       <c r="M17" s="86"/>
@@ -3291,13 +3282,13 @@
     </row>
     <row r="18" spans="1:16" ht="14.4" customHeight="1">
       <c r="A18" s="40" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B18" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>165</v>
+        <v>210</v>
       </c>
       <c r="D18" s="74">
         <v>600000</v>
@@ -3312,13 +3303,13 @@
     </row>
     <row r="19" spans="1:16" ht="14.4" customHeight="1">
       <c r="A19" s="40" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B19" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D19" s="74">
         <v>600000</v>
@@ -3333,13 +3324,13 @@
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" thickBot="1">
       <c r="A20" s="40" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B20" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D20" s="74">
         <v>600000</v>
@@ -3354,13 +3345,13 @@
     </row>
     <row r="21" spans="1:16" ht="14.4" customHeight="1">
       <c r="A21" s="40" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D21" s="74"/>
     </row>
@@ -3431,754 +3422,754 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="66" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B1" s="66" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="67" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B2" s="82" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="68" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B3" s="82" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="67" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B4" s="82" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="67" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B5" s="82" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="68" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B6" s="82" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="67" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B7" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="67" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B8" s="82" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="68" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B9" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="67" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B10" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="68" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B11" s="82" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="68" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B12" s="82" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="68" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B13" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="68" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B14" s="82" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="67" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B15" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="67" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B16" s="82" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="68" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B17" s="82" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="68" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B18" s="82" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="68" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B19" s="82" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="68" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B20" s="82" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="68" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B21" s="82" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="68" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B22" s="82" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="68" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B23" s="82" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="68" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B24" s="82" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="68" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B25" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="68" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B26" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="68" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B27" s="82" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="68" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B28" s="82" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="68" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B29" s="82" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="67" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B30" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="68" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B31" s="82" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="68" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B32" s="82" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="67" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B33" s="82" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="68" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B34" s="82" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="68" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B35" s="82" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="68" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B36" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="68" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B37" s="82" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="68" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B38" s="82" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="68" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B39" s="82" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="68" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B40" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="68" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B41" s="82" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="68" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B42" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="68" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B43" s="82" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="68" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B44" s="82" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="67" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B45" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="68" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B46" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="68" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B47" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="68" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B48" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="68" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B49" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="68" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B50" s="82" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="68" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B51" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="68" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B52" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="68" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B53" s="82" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="67" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B54" s="82" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="68" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B55" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="68" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B56" s="82" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="67" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B57" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="68" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B58" s="82" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="68" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B59" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="68" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B60" s="82" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="68" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B61" s="82" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="68" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B62" s="82" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="68" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B63" s="82" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="68" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B64" s="82" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="68" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B65" s="82" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="68" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B66" s="82" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="69" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B67" s="82" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="69" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B68" s="82" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="68" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B69" s="82" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="68" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B70" s="82" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="68" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B71" s="82" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="68" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B72" s="82" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="68" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B73" s="82" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="68" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B74" s="82" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="68" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B75" s="82" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="68" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B76" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="68" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B77" s="82" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="68" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B78" s="82" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="68" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B79" s="82" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="68" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B80" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="68" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B81" s="82" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="69" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B82" s="82" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="68" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B83" s="82" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="68" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B84" s="82" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="68" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B85" s="82" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="68" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B86" s="82" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="68" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B87" s="82" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="68" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B88" s="82" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="68" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B89" s="82" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="68" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B90" s="82" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="68" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B91" s="82" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="68" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B92" s="82" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="68" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B93" s="82" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="68" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B94" s="82" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -4198,7 +4189,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="82" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -4208,67 +4199,67 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="82" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="82" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="82" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="82" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="82" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="82" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="82" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="82" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="82" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="82" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="82" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="82" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="82" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -4281,18 +4272,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B2">
         <v>518.58000000000004</v>
@@ -4300,7 +4295,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B3">
         <v>153.91999999999999</v>
@@ -4308,7 +4303,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B4">
         <v>270.5</v>
@@ -4316,7 +4311,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B5">
         <v>199.83</v>
@@ -4324,7 +4319,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B6">
         <v>7.92</v>
@@ -4332,7 +4327,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B7">
         <v>501.5</v>
@@ -4340,7 +4335,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B8">
         <v>57.17</v>
@@ -4348,7 +4343,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B9">
         <v>97.5</v>
@@ -4356,7 +4351,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B10">
         <v>225.67</v>
@@ -4364,7 +4359,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B11">
         <v>75.58</v>
@@ -4372,7 +4367,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B12">
         <v>74.75</v>
@@ -4380,7 +4375,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B13">
         <v>152</v>
@@ -4388,7 +4383,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B14">
         <v>431.67</v>
@@ -4396,7 +4391,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B15">
         <v>935.17</v>

--- a/metas.xlsx
+++ b/metas.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="270">
   <si>
     <t>Distribuidor:</t>
   </si>
@@ -347,9 +347,6 @@
     <t>TR</t>
   </si>
   <si>
-    <t>VICTOR CASTILLO</t>
-  </si>
-  <si>
     <t>Meta sucursal</t>
   </si>
   <si>
@@ -404,9 +401,6 @@
     <t>110% &lt; 120%</t>
   </si>
   <si>
-    <t>VICTOR M FLORES</t>
-  </si>
-  <si>
     <t>Sucursal PN</t>
   </si>
   <si>
@@ -470,9 +464,6 @@
     <t>AUX FLEET</t>
   </si>
   <si>
-    <t>BRANDON SALAZAR</t>
-  </si>
-  <si>
     <t>Platino</t>
   </si>
   <si>
@@ -482,9 +473,6 @@
     <t>JEFE SUCURSAL</t>
   </si>
   <si>
-    <t>FRANCISCO GALAVIZ</t>
-  </si>
-  <si>
     <t>Rodio</t>
   </si>
   <si>
@@ -515,12 +503,6 @@
     <t>PN</t>
   </si>
   <si>
-    <t>ANTONIO ALVARADO</t>
-  </si>
-  <si>
-    <t>ERICK FRAUSTO</t>
-  </si>
-  <si>
     <t>HELADIO SANTOS REYES</t>
   </si>
   <si>
@@ -842,24 +824,6 @@
     <t>VICTOR DE JESUS VEGA RODRIGUEZ</t>
   </si>
   <si>
-    <t>ALFREDO PIZAÑA SAMANIEGO</t>
-  </si>
-  <si>
-    <t>MARIO GRANADOS</t>
-  </si>
-  <si>
-    <t>IVAN LOPEZ</t>
-  </si>
-  <si>
-    <t>ALEJANDRO BALTAZAR CISNEROS</t>
-  </si>
-  <si>
-    <t>JOSE ROJAS</t>
-  </si>
-  <si>
-    <t>ANTONIO CRUZ</t>
-  </si>
-  <si>
     <t>NOMBRE_ASESOR</t>
   </si>
   <si>
@@ -867,6 +831,12 @@
   </si>
   <si>
     <t>MANUEL BOTELLO PORTILLO</t>
+  </si>
+  <si>
+    <t>VICTOR HUMBERTO DIAZ CERDA</t>
+  </si>
+  <si>
+    <t>BRANDON DANIEL SALAZAR</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1248,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1467,6 +1437,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="4"/>
@@ -2790,7 +2761,7 @@
         <v>103</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D2" s="74">
         <v>1000000</v>
@@ -2799,29 +2770,29 @@
         <v>37</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H2" s="81"/>
       <c r="I2" s="83" t="s">
+        <v>107</v>
+      </c>
+      <c r="J2" s="61" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="61" t="s">
+      <c r="K2" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="K2" s="63" t="s">
+      <c r="L2" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="L2" s="62" t="s">
+      <c r="M2" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="M2" s="62" t="s">
+      <c r="O2" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="O2" s="64" t="s">
+      <c r="P2" s="64" t="s">
         <v>113</v>
-      </c>
-      <c r="P2" s="64" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="14.4" customHeight="1">
@@ -2829,16 +2800,16 @@
         <v>105</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C3" s="41" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D3" s="74">
         <v>950000</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G3" s="76">
         <v>5000000</v>
@@ -2846,10 +2817,10 @@
       <c r="H3" s="79"/>
       <c r="I3" s="84"/>
       <c r="J3" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="K3" s="47" t="s">
         <v>117</v>
-      </c>
-      <c r="K3" s="47" t="s">
-        <v>118</v>
       </c>
       <c r="L3" s="48">
         <v>0</v>
@@ -2872,13 +2843,13 @@
         <v>104</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D4" s="74">
         <v>900000</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G4" s="76">
         <v>7000000</v>
@@ -2886,10 +2857,10 @@
       <c r="H4" s="79"/>
       <c r="I4" s="84"/>
       <c r="J4" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="K4" s="52" t="s">
         <v>120</v>
-      </c>
-      <c r="K4" s="52" t="s">
-        <v>121</v>
       </c>
       <c r="L4" s="48">
         <v>0.75</v>
@@ -2916,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G5" s="76">
         <v>2100000</v>
@@ -2924,10 +2895,10 @@
       <c r="H5" s="79"/>
       <c r="I5" s="84"/>
       <c r="J5" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="K5" s="52" t="s">
         <v>123</v>
-      </c>
-      <c r="K5" s="52" t="s">
-        <v>124</v>
       </c>
       <c r="L5" s="48">
         <v>1.1000000000000001</v>
@@ -2950,13 +2921,13 @@
         <v>104</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D6" s="74">
         <v>900000</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G6" s="74">
         <v>2100000</v>
@@ -2964,16 +2935,16 @@
       <c r="H6" s="80"/>
       <c r="I6" s="84"/>
       <c r="J6" s="56" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K6" s="52" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L6" s="48">
         <v>1.2</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="O6" s="57">
         <v>1.7500000000000002E-2</v>
@@ -2990,13 +2961,13 @@
         <v>103</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D7" s="74">
         <v>1000000</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G7" s="77">
         <v>16200000</v>
@@ -3005,53 +2976,55 @@
     </row>
     <row r="8" spans="1:16" ht="26.4" customHeight="1">
       <c r="A8" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="74">
+        <v>1200000</v>
+      </c>
+      <c r="I8" s="83" t="s">
+        <v>131</v>
+      </c>
+      <c r="J8" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="K8" s="62" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="74">
-        <v>0</v>
-      </c>
-      <c r="I8" s="83" t="s">
+      <c r="L8" s="65" t="s">
         <v>133</v>
       </c>
-      <c r="J8" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="K8" s="62" t="s">
+      <c r="M8" s="65" t="s">
         <v>134</v>
       </c>
-      <c r="L8" s="65" t="s">
+      <c r="O8" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="M8" s="65" t="s">
+      <c r="P8" s="63" t="s">
         <v>136</v>
-      </c>
-      <c r="O8" s="63" t="s">
-        <v>137</v>
-      </c>
-      <c r="P8" s="63" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="14.4" customHeight="1">
       <c r="A9" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B9" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D9" s="74">
         <v>2000000</v>
       </c>
       <c r="I9" s="84"/>
       <c r="J9" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K9" s="47">
         <v>0</v>
@@ -3071,23 +3044,23 @@
     </row>
     <row r="10" spans="1:16" ht="14.4" customHeight="1">
       <c r="A10" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B10" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D10" s="74">
         <v>950000</v>
       </c>
       <c r="I10" s="84"/>
       <c r="J10" s="51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L10" s="48">
         <v>1.1000000000000001</v>
@@ -3104,23 +3077,23 @@
     </row>
     <row r="11" spans="1:16" ht="14.4" customHeight="1">
       <c r="A11" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B11" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D11" s="74">
         <v>1000000</v>
       </c>
       <c r="I11" s="84"/>
       <c r="J11" s="54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L11" s="48">
         <v>1.2</v>
@@ -3137,21 +3110,21 @@
     </row>
     <row r="12" spans="1:16" ht="14.4" customHeight="1">
       <c r="A12" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="41" t="s">
         <v>142</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="C12" s="41" t="s">
-        <v>144</v>
       </c>
       <c r="D12" s="74"/>
       <c r="I12" s="84"/>
       <c r="J12" s="56" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L12" s="48">
         <v>1.3333333999999999</v>
@@ -3168,22 +3141,22 @@
     </row>
     <row r="13" spans="1:16" ht="14.4" customHeight="1">
       <c r="A13" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>147</v>
+        <v>269</v>
       </c>
       <c r="D13" s="74">
         <v>1000000</v>
       </c>
       <c r="J13" s="58" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L13" s="48">
         <v>1.5</v>
@@ -3194,22 +3167,22 @@
     </row>
     <row r="14" spans="1:16" ht="14.4" customHeight="1">
       <c r="A14" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D14" s="74">
         <v>2200000</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="L14" s="48">
         <v>1.6</v>
@@ -3220,13 +3193,13 @@
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" thickBot="1">
       <c r="A15" s="40" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B15" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D15" s="74">
         <v>1050000</v>
@@ -3240,36 +3213,36 @@
     </row>
     <row r="16" spans="1:16" ht="43.2" customHeight="1" thickBot="1">
       <c r="A16" s="40" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B16" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D16" s="74">
         <v>1050000</v>
       </c>
       <c r="M16" s="85" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="O16" s="63" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="P16" s="63" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="14.4" customHeight="1">
       <c r="A17" s="40" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D17" s="74"/>
       <c r="M17" s="86"/>
@@ -3282,13 +3255,13 @@
     </row>
     <row r="18" spans="1:16" ht="14.4" customHeight="1">
       <c r="A18" s="40" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B18" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D18" s="74">
         <v>600000</v>
@@ -3303,13 +3276,13 @@
     </row>
     <row r="19" spans="1:16" ht="14.4" customHeight="1">
       <c r="A19" s="40" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B19" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D19" s="74">
         <v>600000</v>
@@ -3324,13 +3297,13 @@
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" thickBot="1">
       <c r="A20" s="40" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B20" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D20" s="74">
         <v>600000</v>
@@ -3345,13 +3318,13 @@
     </row>
     <row r="21" spans="1:16" ht="14.4" customHeight="1">
       <c r="A21" s="40" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D21" s="74"/>
     </row>
@@ -3422,754 +3395,754 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="66" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B1" s="66" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="67" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B2" s="82" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="68" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B3" s="82" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="67" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B4" s="82" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="67" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B5" s="82" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="68" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B6" s="82" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="67" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B7" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="67" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B8" s="82" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="68" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B9" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="67" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B10" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="68" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B11" s="82" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="68" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B12" s="82" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="68" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B13" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="68" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B14" s="82" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="67" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B15" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="67" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B16" s="82" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="68" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B17" s="82" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="68" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B18" s="82" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="68" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B19" s="82" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="68" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B20" s="82" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="68" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B21" s="82" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="68" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B22" s="82" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="68" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B23" s="82" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="68" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B24" s="82" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="68" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B25" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="68" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B26" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="68" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B27" s="82" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="68" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B28" s="82" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="68" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B29" s="82" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="67" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B30" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="68" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B31" s="82" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="68" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B32" s="82" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="67" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B33" s="82" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="68" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B34" s="82" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="68" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B35" s="82" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="68" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B36" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="68" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B37" s="82" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="68" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B38" s="82" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="68" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B39" s="82" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="68" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B40" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="68" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B41" s="82" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="68" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B42" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="68" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B43" s="82" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="68" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B44" s="82" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="67" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B45" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="68" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B46" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="68" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B47" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="68" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B48" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="68" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B49" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="68" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B50" s="82" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="68" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B51" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="68" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B52" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="68" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B53" s="82" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="67" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B54" s="82" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="68" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B55" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="68" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B56" s="82" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="67" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B57" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="68" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B58" s="82" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="68" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B59" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="68" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B60" s="82" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="68" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B61" s="82" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="68" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B62" s="82" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="68" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B63" s="82" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="68" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B64" s="82" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="68" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B65" s="82" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="68" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B66" s="82" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="69" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B67" s="82" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="69" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B68" s="82" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="68" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B69" s="82" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="68" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B70" s="82" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="68" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B71" s="82" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="68" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B72" s="82" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="68" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B73" s="82" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="68" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B74" s="82" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="68" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B75" s="82" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="68" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B76" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="68" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B77" s="82" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="68" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B78" s="82" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="68" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B79" s="82" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="68" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B80" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="68" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B81" s="82" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="69" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B82" s="82" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="68" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B83" s="82" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="68" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B84" s="82" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="68" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B85" s="82" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="68" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B86" s="82" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="68" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B87" s="82" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="68" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B88" s="82" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="68" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B89" s="82" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="68" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B90" s="82" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="68" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B91" s="82" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="68" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B92" s="82" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="68" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B93" s="82" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="68" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B94" s="82" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -4181,85 +4154,90 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="23.5" style="60" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="82" t="s">
+    <row r="1" spans="1:1" ht="14.4">
+      <c r="A1" s="88" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="14.4">
+      <c r="A2" s="88" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="14.4">
+      <c r="A3" s="88" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="14.4">
+      <c r="A4" s="88" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="14.4">
+      <c r="A5" s="88" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="14.4">
+      <c r="A6" s="88" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="14.4">
+      <c r="A7" s="88" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="14.4">
+      <c r="A8" s="88" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="14.4">
+      <c r="A9" s="88" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="14.4">
+      <c r="A10" s="88" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="14.4">
+      <c r="A11" s="88" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="14.4">
+      <c r="A12" s="88" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="82" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="82" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="82" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="82" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="82" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="82" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="82" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="82" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="82" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="82" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="82" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="82" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="82" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="82" t="s">
-        <v>276</v>
+    <row r="13" spans="1:1" ht="14.4">
+      <c r="A13" s="88" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="14.4">
+      <c r="A14" s="88" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="14.4">
+      <c r="A15" s="88" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="14.4">
+      <c r="A16" s="88" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -4279,15 +4257,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B2">
         <v>518.58000000000004</v>
@@ -4295,7 +4273,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B3">
         <v>153.91999999999999</v>
@@ -4303,7 +4281,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B4">
         <v>270.5</v>
@@ -4311,7 +4289,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B5">
         <v>199.83</v>
@@ -4319,7 +4297,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B6">
         <v>7.92</v>
@@ -4327,7 +4305,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B7">
         <v>501.5</v>
@@ -4335,7 +4313,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B8">
         <v>57.17</v>
@@ -4343,7 +4321,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B9">
         <v>97.5</v>
@@ -4351,7 +4329,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B10">
         <v>225.67</v>
@@ -4359,7 +4337,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B11">
         <v>75.58</v>
@@ -4367,7 +4345,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B12">
         <v>74.75</v>
@@ -4375,7 +4353,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B13">
         <v>152</v>
@@ -4383,7 +4361,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B14">
         <v>431.67</v>
@@ -4391,7 +4369,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B15">
         <v>935.17</v>

--- a/metas.xlsx
+++ b/metas.xlsx
@@ -1428,6 +1428,7 @@
     <xf numFmtId="44" fontId="21" fillId="14" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -1437,7 +1438,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="4"/>
@@ -2773,7 +2773,7 @@
         <v>106</v>
       </c>
       <c r="H2" s="81"/>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="84" t="s">
         <v>107</v>
       </c>
       <c r="J2" s="61" t="s">
@@ -2815,7 +2815,7 @@
         <v>5000000</v>
       </c>
       <c r="H3" s="79"/>
-      <c r="I3" s="84"/>
+      <c r="I3" s="85"/>
       <c r="J3" s="46" t="s">
         <v>116</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>7000000</v>
       </c>
       <c r="H4" s="79"/>
-      <c r="I4" s="84"/>
+      <c r="I4" s="85"/>
       <c r="J4" s="51" t="s">
         <v>119</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>2100000</v>
       </c>
       <c r="H5" s="79"/>
-      <c r="I5" s="84"/>
+      <c r="I5" s="85"/>
       <c r="J5" s="54" t="s">
         <v>122</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>2100000</v>
       </c>
       <c r="H6" s="80"/>
-      <c r="I6" s="84"/>
+      <c r="I6" s="85"/>
       <c r="J6" s="56" t="s">
         <v>125</v>
       </c>
@@ -2987,7 +2987,7 @@
       <c r="D8" s="74">
         <v>1200000</v>
       </c>
-      <c r="I8" s="83" t="s">
+      <c r="I8" s="84" t="s">
         <v>131</v>
       </c>
       <c r="J8" s="61" t="s">
@@ -3017,12 +3017,12 @@
         <v>103</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="D9" s="74">
         <v>2000000</v>
       </c>
-      <c r="I9" s="84"/>
+      <c r="I9" s="85"/>
       <c r="J9" s="46" t="s">
         <v>116</v>
       </c>
@@ -3055,7 +3055,7 @@
       <c r="D10" s="74">
         <v>950000</v>
       </c>
-      <c r="I10" s="84"/>
+      <c r="I10" s="85"/>
       <c r="J10" s="51" t="s">
         <v>119</v>
       </c>
@@ -3088,7 +3088,7 @@
       <c r="D11" s="74">
         <v>1000000</v>
       </c>
-      <c r="I11" s="84"/>
+      <c r="I11" s="85"/>
       <c r="J11" s="54" t="s">
         <v>122</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>142</v>
       </c>
       <c r="D12" s="74"/>
-      <c r="I12" s="84"/>
+      <c r="I12" s="85"/>
       <c r="J12" s="56" t="s">
         <v>125</v>
       </c>
@@ -3224,7 +3224,7 @@
       <c r="D16" s="74">
         <v>1050000</v>
       </c>
-      <c r="M16" s="85" t="s">
+      <c r="M16" s="86" t="s">
         <v>153</v>
       </c>
       <c r="O16" s="63" t="s">
@@ -3245,7 +3245,7 @@
         <v>156</v>
       </c>
       <c r="D17" s="74"/>
-      <c r="M17" s="86"/>
+      <c r="M17" s="87"/>
       <c r="O17" s="50">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -3266,7 +3266,7 @@
       <c r="D18" s="74">
         <v>600000</v>
       </c>
-      <c r="M18" s="86"/>
+      <c r="M18" s="87"/>
       <c r="O18" s="53">
         <v>1.6500000000000001E-2</v>
       </c>
@@ -3287,7 +3287,7 @@
       <c r="D19" s="74">
         <v>600000</v>
       </c>
-      <c r="M19" s="86"/>
+      <c r="M19" s="87"/>
       <c r="O19" s="55">
         <v>1.95E-2</v>
       </c>
@@ -3308,7 +3308,7 @@
       <c r="D20" s="74">
         <v>600000</v>
       </c>
-      <c r="M20" s="87"/>
+      <c r="M20" s="88"/>
       <c r="O20" s="57">
         <v>2.2499999999999999E-2</v>
       </c>
@@ -4161,82 +4161,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="14.4">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="83" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="14.4">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="83" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="14.4">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="83" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="14.4">
-      <c r="A4" s="88" t="s">
+      <c r="A4" s="83" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="14.4">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="83" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="14.4">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="83" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="14.4">
-      <c r="A7" s="88" t="s">
+      <c r="A7" s="83" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="14.4">
-      <c r="A8" s="88" t="s">
+      <c r="A8" s="83" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="14.4">
-      <c r="A9" s="88" t="s">
+      <c r="A9" s="83" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="14.4">
-      <c r="A10" s="88" t="s">
+      <c r="A10" s="83" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="14.4">
-      <c r="A11" s="88" t="s">
+      <c r="A11" s="83" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="14.4">
-      <c r="A12" s="88" t="s">
+      <c r="A12" s="83" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="14.4">
-      <c r="A13" s="88" t="s">
+      <c r="A13" s="83" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="14.4">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="83" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="14.4">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="83" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="14.4">
-      <c r="A16" s="88" t="s">
+      <c r="A16" s="83" t="s">
         <v>158</v>
       </c>
     </row>

--- a/metas.xlsx
+++ b/metas.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoamher-my.sharepoint.com/personal/carlos_lozano_amher_com_mx/Documents/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12312" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12312" firstSheet="5" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Estructura de ventas" sheetId="1" r:id="rId1"/>
@@ -17,17 +17,34 @@
     <sheet name="CARTERA" sheetId="3" r:id="rId3"/>
     <sheet name="Hoja1" sheetId="4" r:id="rId4"/>
     <sheet name="ACEITE_BASE" sheetId="5" r:id="rId5"/>
+    <sheet name="NVOS OBJ VENTA AGO 2026" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CARTERA!$A$1:$B$94</definedName>
     <definedName name="status">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="274">
   <si>
     <t>Distribuidor:</t>
   </si>
@@ -347,6 +364,9 @@
     <t>TR</t>
   </si>
   <si>
+    <t>VICTOR EDUARDO CASTILLO GARCIA</t>
+  </si>
+  <si>
     <t>Meta sucursal</t>
   </si>
   <si>
@@ -374,6 +394,9 @@
     <t>TELEMARKETING</t>
   </si>
   <si>
+    <t>JOSE VENTURA ROJAS DIAZ</t>
+  </si>
+  <si>
     <t>Sucursal TR</t>
   </si>
   <si>
@@ -383,6 +406,9 @@
     <t>&lt; 75%</t>
   </si>
   <si>
+    <t>MANUEL BOTELLO PORTILLO</t>
+  </si>
+  <si>
     <t>sucursal GP</t>
   </si>
   <si>
@@ -401,6 +427,9 @@
     <t>110% &lt; 120%</t>
   </si>
   <si>
+    <t>VICTOR MANUEL FLORES LOPEZ</t>
+  </si>
+  <si>
     <t>Sucursal PN</t>
   </si>
   <si>
@@ -422,6 +451,9 @@
     <t>GP</t>
   </si>
   <si>
+    <t>VICTOR HUMBERTO DIAZ CERDA</t>
+  </si>
+  <si>
     <t>GRUPAL</t>
   </si>
   <si>
@@ -440,403 +472,400 @@
     <t>Factor Grupal Mostrador</t>
   </si>
   <si>
+    <t>CESAR ALEJANDRO BALTAZAR CISNEROS</t>
+  </si>
+  <si>
+    <t>HUGO ALBERTO BERNAL CASTILLO</t>
+  </si>
+  <si>
+    <t>ALFREDO PIZANA SAMANIEGO</t>
+  </si>
+  <si>
+    <t>120% &lt; 133%</t>
+  </si>
+  <si>
+    <t>TRC</t>
+  </si>
+  <si>
+    <t>LEADS</t>
+  </si>
+  <si>
+    <t>IRLANDA SANCHEZ</t>
+  </si>
+  <si>
+    <t>133% &lt; 150%</t>
+  </si>
+  <si>
+    <t>AUX FLEET</t>
+  </si>
+  <si>
+    <t>BRANDON DANIEL SALAZAR</t>
+  </si>
+  <si>
+    <t>Platino</t>
+  </si>
+  <si>
+    <t>&gt;= 160%</t>
+  </si>
+  <si>
+    <t>JEFE SUCURSAL</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER GALAVIZ RUELAS</t>
+  </si>
+  <si>
+    <t>Rodio</t>
+  </si>
+  <si>
+    <t>&gt;= 170%</t>
+  </si>
+  <si>
+    <t>MONC</t>
+  </si>
+  <si>
+    <t>ESTEBAN BRIONES LARA</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO FLORES PEREZ</t>
+  </si>
+  <si>
+    <t>FACTORES SUMADOS INDIVIDUAL + GRUPAL</t>
+  </si>
+  <si>
+    <t>Factores sumados Calle</t>
+  </si>
+  <si>
+    <t>Factores sumados Mostrador</t>
+  </si>
+  <si>
+    <t>MIRNA CONSUELO CEPEDA LERMA</t>
+  </si>
+  <si>
+    <t>PN</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO ALVARADO VILLANUEVA</t>
+  </si>
+  <si>
+    <t>ERICK IVAN FRAUSTO CORTEZ</t>
+  </si>
+  <si>
+    <t>HELADIO SANTOS REYES</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVO</t>
+  </si>
+  <si>
+    <t>MOSTRADOR PN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cliente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendedor </t>
+  </si>
+  <si>
+    <t>FLEET SERVICE LALA</t>
+  </si>
+  <si>
+    <t>CONSOLIDAMEX</t>
+  </si>
+  <si>
+    <t>FLEET SERVICE CCN</t>
+  </si>
+  <si>
+    <t>FLEET SERVICE GEN INDUSTRIAL</t>
+  </si>
+  <si>
+    <t>PAMESA DE LA LAGUNA</t>
+  </si>
+  <si>
+    <t>FLEET SERVICE COPPEL REFACCIONES</t>
+  </si>
+  <si>
+    <t>FLEET SERVICE PASA TORREÓN</t>
+  </si>
+  <si>
+    <t>RANCHO LUCERO</t>
+  </si>
+  <si>
+    <t>FLEET SERVICE QUÁLITAS</t>
+  </si>
+  <si>
+    <t>JIBE CONSTRUCCIONES Y PAVIMENTOS</t>
+  </si>
+  <si>
+    <t>ALEJANDRA ESQUIVEL FERNANDEZ</t>
+  </si>
+  <si>
+    <t>TRANSPORTES Y SERVICIOS PATRI</t>
+  </si>
+  <si>
+    <t>TRANSPORTES VILLARREAL BERLANGA</t>
+  </si>
+  <si>
+    <t>FLEET SERVICE BARCEL</t>
+  </si>
+  <si>
+    <t>FLEET SERVICE SIMSA</t>
+  </si>
+  <si>
+    <t>TRANSPORTES ESPECIALIZADOS LUCERO</t>
+  </si>
+  <si>
+    <t>MAVERICK EXPRESS CARRIERS LLC</t>
+  </si>
+  <si>
+    <t>TRANSPORTES MINEROS DE COAHUILA</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA DE RENDIMIENTOS DE LA LAGUNA</t>
+  </si>
+  <si>
+    <t>RADO IMPORTACIONES</t>
+  </si>
+  <si>
+    <t>ROJO LOGISTIC</t>
+  </si>
+  <si>
+    <t>MAS PORTEO</t>
+  </si>
+  <si>
+    <t>TRANSPORTES BRECA</t>
+  </si>
+  <si>
+    <t>TRANSPORTES GARZA LEAL</t>
+  </si>
+  <si>
+    <t>TRANSPORTES COLMAR</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA ALPURA</t>
+  </si>
+  <si>
+    <t>CIRCULO RECOLECTOR</t>
+  </si>
+  <si>
+    <t>RICARDO FLORES</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER CALDERON RECIO</t>
+  </si>
+  <si>
+    <t>FLEET SERVICE CEMEX TRANSPORTE</t>
+  </si>
+  <si>
+    <t>SISTEMAS DE APOYO LOGISTICO AL COMERCIO INTERNACIO</t>
+  </si>
+  <si>
+    <t>TCI TRANSPORTES</t>
+  </si>
+  <si>
+    <t>FLEET SERVICE TRANSMONTES</t>
+  </si>
+  <si>
+    <t>LINEAS 1° DE MAYO</t>
+  </si>
+  <si>
+    <t>TRANSINTERNACIONAL</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA DE LA LAGUNA</t>
+  </si>
+  <si>
+    <t>PAYSA TRANSPORTES</t>
+  </si>
+  <si>
+    <t>ERVEY ALVAREZ HUERTA</t>
+  </si>
+  <si>
+    <t>AUTOLINEAS MRD</t>
+  </si>
+  <si>
+    <t>TRANSPORTES FORANEOS Y LOCALES DE RIO GRANDE</t>
+  </si>
+  <si>
+    <t>AGRICOLA EL EDEN</t>
+  </si>
+  <si>
+    <t>BETA SANTA MONICA</t>
+  </si>
+  <si>
+    <t>COMPAÑIA HARINERA DE LA LAGUNA</t>
+  </si>
+  <si>
+    <t>METALURGICA MET-MEX PEÑOLES</t>
+  </si>
+  <si>
+    <t>FLEET SERVICE GNP</t>
+  </si>
+  <si>
+    <t>FLETES CHILCHOTA</t>
+  </si>
+  <si>
+    <t>CARTA BLANCA LAGUNERA</t>
+  </si>
+  <si>
+    <t>DUMA TRANSPORTES</t>
+  </si>
+  <si>
+    <t>SUPERIOR MEAT COMPANY</t>
+  </si>
+  <si>
+    <t>AUTOMOTRIZ GALVAN Y MUZQUIZ</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA DE LIQUIDOS AZTECA</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL ARMENDARIZ GARCIA</t>
+  </si>
+  <si>
+    <t>SUPER GUTIERREZ</t>
+  </si>
+  <si>
+    <t>FLEET SERVICE PASA ACUÑA</t>
+  </si>
+  <si>
+    <t>HERMANOS BATTA</t>
+  </si>
+  <si>
+    <t>AUTOBUSES UNION</t>
+  </si>
+  <si>
+    <t>FLEET SERVICE CEMEX CONCRETOS</t>
+  </si>
+  <si>
+    <t>SOLUCIONES DE TRANSPORTE DE PERSONAL</t>
+  </si>
+  <si>
+    <t>EMBRAGUES Y FRENOS DE LA LAGUNA</t>
+  </si>
+  <si>
+    <t>TRANSERVICIOS</t>
+  </si>
+  <si>
+    <t>TRANSPORTE ESPECIALIZADO ELISEO</t>
+  </si>
+  <si>
+    <t>MARIA MONICA SANCHEZ LOZANO</t>
+  </si>
+  <si>
+    <t>SERVICIOS GTA</t>
+  </si>
+  <si>
+    <t>TRANSPORTACIONES Y COMERCIALIZADORA DAGO</t>
+  </si>
+  <si>
+    <t>COERSA LOGISTICA</t>
+  </si>
+  <si>
+    <t>JOAQUIN VILLANUEVA HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JOSE BELISARIO RUBIO ARIZPE</t>
+  </si>
+  <si>
+    <t>OSCAR CRISTO ZAMARRIPA DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>CONCRETOS VISION</t>
+  </si>
+  <si>
+    <t>JUAN GABRIEL MENDEZ VILLARREAL</t>
+  </si>
+  <si>
+    <t>RICARDO ALBERTO MARCOS BUGARIN</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA DE COMBUSTIBLES LAGUNA</t>
+  </si>
+  <si>
+    <t>RANCHO SANTO TOMAS</t>
+  </si>
+  <si>
+    <t>JUAN GABRIEL DE LA TORRE SANCHEZ</t>
+  </si>
+  <si>
+    <t>TURISMO TITO@C39S</t>
+  </si>
+  <si>
+    <t>FERNANDO LOPEZ DELGADILLO</t>
+  </si>
+  <si>
+    <t>EDUARDO ANTONIO TRICIO SIERRA</t>
+  </si>
+  <si>
+    <t>TRANSPORTES RIOJAS GONZALEZ</t>
+  </si>
+  <si>
+    <t>SERVICIOS EMPRESARIALES UNION</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA REME DE LA LAGUNA</t>
+  </si>
+  <si>
+    <t>R.V. RECICLADOS</t>
+  </si>
+  <si>
+    <t>SETSA TRASNPORTES</t>
+  </si>
+  <si>
+    <t>GD APPAREL</t>
+  </si>
+  <si>
+    <t>PREMEZCLADOS NAZAS</t>
+  </si>
+  <si>
+    <t>OSCAR JAVIER JIMENEZ PEREZ</t>
+  </si>
+  <si>
+    <t>RAYMUNDO VALENZUELA CHAIREZ</t>
+  </si>
+  <si>
+    <t>MIDORY GALVAN BERNAL</t>
+  </si>
+  <si>
+    <t>LUIS DEL VILLAR GARCIA</t>
+  </si>
+  <si>
+    <t>BLANCA XOCHITL CAVANZON SILOS</t>
+  </si>
+  <si>
+    <t>QUIMICA DEL REY</t>
+  </si>
+  <si>
+    <t>GRUPO CONCRETOS</t>
+  </si>
+  <si>
+    <t>OSCAR RENE RODRIGUEZ FLORES</t>
+  </si>
+  <si>
+    <t>MARIA LUISA ORTIZ CISNEROS</t>
+  </si>
+  <si>
+    <t>VICTOR DE JESUS VEGA RODRIGUEZ</t>
+  </si>
+  <si>
     <t>CÉSAR ALEJANDRO BALTAZAR CISNEROS</t>
   </si>
   <si>
-    <t>HUGO ALBERTO BERNAL CASTILLO</t>
-  </si>
-  <si>
-    <t>120% &lt; 133%</t>
-  </si>
-  <si>
-    <t>TRC</t>
-  </si>
-  <si>
-    <t>LEADS</t>
-  </si>
-  <si>
-    <t>IRLANDA SANCHEZ</t>
-  </si>
-  <si>
-    <t>133% &lt; 150%</t>
-  </si>
-  <si>
-    <t>AUX FLEET</t>
-  </si>
-  <si>
-    <t>Platino</t>
-  </si>
-  <si>
-    <t>&gt;= 160%</t>
-  </si>
-  <si>
-    <t>JEFE SUCURSAL</t>
-  </si>
-  <si>
-    <t>Rodio</t>
-  </si>
-  <si>
-    <t>&gt;= 170%</t>
-  </si>
-  <si>
-    <t>MONC</t>
-  </si>
-  <si>
-    <t>ESTEBAN BRIONES LARA</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO FLORES PEREZ</t>
-  </si>
-  <si>
-    <t>FACTORES SUMADOS INDIVIDUAL + GRUPAL</t>
-  </si>
-  <si>
-    <t>Factores sumados Calle</t>
-  </si>
-  <si>
-    <t>Factores sumados Mostrador</t>
-  </si>
-  <si>
-    <t>MIRNA CONSUELO CEPEDA LERMA</t>
-  </si>
-  <si>
-    <t>PN</t>
-  </si>
-  <si>
-    <t>HELADIO SANTOS REYES</t>
-  </si>
-  <si>
-    <t>ADMINISTRATIVO</t>
-  </si>
-  <si>
-    <t>MOSTRADOR PN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cliente </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendedor </t>
-  </si>
-  <si>
-    <t>FLEET SERVICE LALA</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER GALAVIZ RUELAS</t>
-  </si>
-  <si>
-    <t>CONSOLIDAMEX</t>
-  </si>
-  <si>
-    <t>VICTOR EDUARDO CASTILLO GARCIA</t>
-  </si>
-  <si>
-    <t>FLEET SERVICE CCN</t>
-  </si>
-  <si>
-    <t>ALFREDO PIZANA SAMANIEGO</t>
-  </si>
-  <si>
-    <t>FLEET SERVICE GEN INDUSTRIAL</t>
-  </si>
-  <si>
-    <t>PAMESA DE LA LAGUNA</t>
-  </si>
-  <si>
-    <t>FLEET SERVICE COPPEL REFACCIONES</t>
-  </si>
-  <si>
-    <t>CESAR ALEJANDRO BALTAZAR CISNEROS</t>
-  </si>
-  <si>
-    <t>FLEET SERVICE PASA TORREÓN</t>
-  </si>
-  <si>
-    <t>RANCHO LUCERO</t>
-  </si>
-  <si>
-    <t>FLEET SERVICE QUÁLITAS</t>
-  </si>
-  <si>
-    <t>JIBE CONSTRUCCIONES Y PAVIMENTOS</t>
-  </si>
-  <si>
-    <t>ALEJANDRA ESQUIVEL FERNANDEZ</t>
-  </si>
-  <si>
-    <t>ERICK IVAN FRAUSTO CORTEZ</t>
-  </si>
-  <si>
-    <t>TRANSPORTES Y SERVICIOS PATRI</t>
-  </si>
-  <si>
-    <t>TRANSPORTES VILLARREAL BERLANGA</t>
-  </si>
-  <si>
-    <t>JOSE VENTURA ROJAS DIAZ</t>
-  </si>
-  <si>
-    <t>FLEET SERVICE BARCEL</t>
-  </si>
-  <si>
-    <t>FLEET SERVICE SIMSA</t>
-  </si>
-  <si>
-    <t>TRANSPORTES ESPECIALIZADOS LUCERO</t>
-  </si>
-  <si>
-    <t>MAVERICK EXPRESS CARRIERS LLC</t>
-  </si>
-  <si>
-    <t>TRANSPORTES MINEROS DE COAHUILA</t>
-  </si>
-  <si>
-    <t>TRANSPORTADORA DE RENDIMIENTOS DE LA LAGUNA</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL FLORES LOPEZ</t>
-  </si>
-  <si>
-    <t>RADO IMPORTACIONES</t>
-  </si>
-  <si>
-    <t>ROJO LOGISTIC</t>
-  </si>
-  <si>
-    <t>MAS PORTEO</t>
-  </si>
-  <si>
-    <t>TRANSPORTES BRECA</t>
-  </si>
-  <si>
-    <t>TRANSPORTES GARZA LEAL</t>
-  </si>
-  <si>
-    <t>TRANSPORTES COLMAR</t>
-  </si>
-  <si>
-    <t>TRANSPORTADORA ALPURA</t>
-  </si>
-  <si>
-    <t>CIRCULO RECOLECTOR</t>
-  </si>
-  <si>
-    <t>RICARDO FLORES</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER CALDERON RECIO</t>
-  </si>
-  <si>
-    <t>FLEET SERVICE CEMEX TRANSPORTE</t>
-  </si>
-  <si>
-    <t>SISTEMAS DE APOYO LOGISTICO AL COMERCIO INTERNACIO</t>
-  </si>
-  <si>
-    <t>TCI TRANSPORTES</t>
-  </si>
-  <si>
-    <t>FLEET SERVICE TRANSMONTES</t>
-  </si>
-  <si>
-    <t>LINEAS 1° DE MAYO</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO ALVARADO VILLANUEVA</t>
-  </si>
-  <si>
-    <t>TRANSINTERNACIONAL</t>
-  </si>
-  <si>
-    <t>TRANSPORTADORA DE LA LAGUNA</t>
-  </si>
-  <si>
-    <t>PAYSA TRANSPORTES</t>
-  </si>
-  <si>
-    <t>ERVEY ALVAREZ HUERTA</t>
-  </si>
-  <si>
-    <t>AUTOLINEAS MRD</t>
-  </si>
-  <si>
-    <t>TRANSPORTES FORANEOS Y LOCALES DE RIO GRANDE</t>
-  </si>
-  <si>
-    <t>AGRICOLA EL EDEN</t>
-  </si>
-  <si>
-    <t>BETA SANTA MONICA</t>
-  </si>
-  <si>
-    <t>COMPAÑIA HARINERA DE LA LAGUNA</t>
-  </si>
-  <si>
-    <t>METALURGICA MET-MEX PEÑOLES</t>
-  </si>
-  <si>
-    <t>FLEET SERVICE GNP</t>
-  </si>
-  <si>
-    <t>FLETES CHILCHOTA</t>
-  </si>
-  <si>
-    <t>CARTA BLANCA LAGUNERA</t>
-  </si>
-  <si>
-    <t>DUMA TRANSPORTES</t>
-  </si>
-  <si>
-    <t>SUPERIOR MEAT COMPANY</t>
-  </si>
-  <si>
-    <t>AUTOMOTRIZ GALVAN Y MUZQUIZ</t>
-  </si>
-  <si>
-    <t>TRANSPORTADORA DE LIQUIDOS AZTECA</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL ARMENDARIZ GARCIA</t>
-  </si>
-  <si>
-    <t>SUPER GUTIERREZ</t>
-  </si>
-  <si>
-    <t>FLEET SERVICE PASA ACUÑA</t>
-  </si>
-  <si>
-    <t>HERMANOS BATTA</t>
-  </si>
-  <si>
-    <t>AUTOBUSES UNION</t>
-  </si>
-  <si>
-    <t>FLEET SERVICE CEMEX CONCRETOS</t>
-  </si>
-  <si>
-    <t>SOLUCIONES DE TRANSPORTE DE PERSONAL</t>
-  </si>
-  <si>
-    <t>EMBRAGUES Y FRENOS DE LA LAGUNA</t>
-  </si>
-  <si>
-    <t>TRANSERVICIOS</t>
-  </si>
-  <si>
-    <t>TRANSPORTE ESPECIALIZADO ELISEO</t>
-  </si>
-  <si>
-    <t>MARIA MONICA SANCHEZ LOZANO</t>
-  </si>
-  <si>
-    <t>SERVICIOS GTA</t>
-  </si>
-  <si>
-    <t>TRANSPORTACIONES Y COMERCIALIZADORA DAGO</t>
-  </si>
-  <si>
-    <t>COERSA LOGISTICA</t>
-  </si>
-  <si>
-    <t>JOAQUIN VILLANUEVA HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JOSE BELISARIO RUBIO ARIZPE</t>
-  </si>
-  <si>
-    <t>OSCAR CRISTO ZAMARRIPA DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>CONCRETOS VISION</t>
-  </si>
-  <si>
-    <t>JUAN GABRIEL MENDEZ VILLARREAL</t>
-  </si>
-  <si>
-    <t>RICARDO ALBERTO MARCOS BUGARIN</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA DE COMBUSTIBLES LAGUNA</t>
-  </si>
-  <si>
-    <t>RANCHO SANTO TOMAS</t>
-  </si>
-  <si>
-    <t>JUAN GABRIEL DE LA TORRE SANCHEZ</t>
-  </si>
-  <si>
-    <t>TURISMO TITO@C39S</t>
-  </si>
-  <si>
-    <t>FERNANDO LOPEZ DELGADILLO</t>
-  </si>
-  <si>
-    <t>EDUARDO ANTONIO TRICIO SIERRA</t>
-  </si>
-  <si>
-    <t>TRANSPORTES RIOJAS GONZALEZ</t>
-  </si>
-  <si>
-    <t>SERVICIOS EMPRESARIALES UNION</t>
-  </si>
-  <si>
-    <t>TRANSPORTADORA REME DE LA LAGUNA</t>
-  </si>
-  <si>
-    <t>R.V. RECICLADOS</t>
-  </si>
-  <si>
-    <t>SETSA TRASNPORTES</t>
-  </si>
-  <si>
-    <t>GD APPAREL</t>
-  </si>
-  <si>
-    <t>PREMEZCLADOS NAZAS</t>
-  </si>
-  <si>
-    <t>OSCAR JAVIER JIMENEZ PEREZ</t>
-  </si>
-  <si>
-    <t>RAYMUNDO VALENZUELA CHAIREZ</t>
-  </si>
-  <si>
-    <t>MIDORY GALVAN BERNAL</t>
-  </si>
-  <si>
-    <t>LUIS DEL VILLAR GARCIA</t>
-  </si>
-  <si>
-    <t>BLANCA XOCHITL CAVANZON SILOS</t>
-  </si>
-  <si>
-    <t>QUIMICA DEL REY</t>
-  </si>
-  <si>
-    <t>GRUPO CONCRETOS</t>
-  </si>
-  <si>
-    <t>OSCAR RENE RODRIGUEZ FLORES</t>
-  </si>
-  <si>
-    <t>MARIA LUISA ORTIZ CISNEROS</t>
-  </si>
-  <si>
-    <t>VICTOR DE JESUS VEGA RODRIGUEZ</t>
-  </si>
-  <si>
     <t>NOMBRE_ASESOR</t>
   </si>
   <si>
     <t>PROMEDIO_LITROS_2025</t>
   </si>
   <si>
-    <t>MANUEL BOTELLO PORTILLO</t>
-  </si>
-  <si>
-    <t>VICTOR HUMBERTO DIAZ CERDA</t>
-  </si>
-  <si>
-    <t>BRANDON DANIEL SALAZAR</t>
+    <t>NUEVO SEPT 2026</t>
+  </si>
+  <si>
+    <t>Nueva Meta Sept 2026</t>
+  </si>
+  <si>
+    <t>JESUS ALFONSO CARLOS FERNANDEZ</t>
+  </si>
+  <si>
+    <t>JESUS ARTURO CALDERON</t>
   </si>
 </sst>
 </file>
@@ -851,7 +880,7 @@
     <numFmt numFmtId="166" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1017,6 +1046,18 @@
       <sz val="8"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1248,7 +1289,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1379,7 +1420,6 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1428,16 +1468,20 @@
     <xf numFmtId="44" fontId="21" fillId="14" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="4"/>
@@ -1782,13 +1826,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.09765625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="16.796875" style="60" customWidth="1"/>
-    <col min="3" max="3" width="35.3984375" style="60" customWidth="1"/>
-    <col min="4" max="4" width="33.19921875" style="60" customWidth="1"/>
+    <col min="2" max="2" width="16.8984375" customWidth="1"/>
+    <col min="3" max="3" width="35.3984375" customWidth="1"/>
+    <col min="4" max="4" width="33.09765625" customWidth="1"/>
     <col min="5" max="5" width="20" style="3" customWidth="1"/>
-    <col min="6" max="6" width="30.19921875" style="60" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.6" customHeight="1">
@@ -1984,7 +2028,7 @@
       <c r="C16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="71">
+      <c r="D16" s="70">
         <v>1</v>
       </c>
     </row>
@@ -1995,7 +2039,7 @@
       <c r="C17" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="71">
+      <c r="D17" s="70">
         <v>6</v>
       </c>
     </row>
@@ -2006,7 +2050,7 @@
       <c r="C18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="71">
+      <c r="D18" s="70">
         <v>2</v>
       </c>
     </row>
@@ -2017,7 +2061,7 @@
       <c r="C19" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="71">
+      <c r="D19" s="70">
         <v>2</v>
       </c>
     </row>
@@ -2028,7 +2072,7 @@
       <c r="C20" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="71">
+      <c r="D20" s="70">
         <v>2</v>
       </c>
     </row>
@@ -2039,7 +2083,7 @@
       <c r="C21" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="71">
+      <c r="D21" s="70">
         <v>10</v>
       </c>
     </row>
@@ -2050,7 +2094,7 @@
       <c r="C22" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="71">
+      <c r="D22" s="70">
         <v>7</v>
       </c>
     </row>
@@ -2234,7 +2278,7 @@
       <c r="C35" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D35" s="72">
+      <c r="D35" s="71">
         <v>2</v>
       </c>
     </row>
@@ -2245,7 +2289,7 @@
       <c r="C36" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D36" s="72">
+      <c r="D36" s="71">
         <v>5</v>
       </c>
     </row>
@@ -2256,7 +2300,7 @@
       <c r="C37" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="72">
+      <c r="D37" s="71">
         <v>3</v>
       </c>
     </row>
@@ -2267,7 +2311,7 @@
       <c r="C38" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D38" s="72">
+      <c r="D38" s="71">
         <v>4</v>
       </c>
     </row>
@@ -2278,7 +2322,7 @@
       <c r="C39" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="72">
+      <c r="D39" s="71">
         <v>3</v>
       </c>
     </row>
@@ -2289,7 +2333,7 @@
       <c r="C40" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D40" s="72">
+      <c r="D40" s="71">
         <v>11</v>
       </c>
     </row>
@@ -2300,7 +2344,7 @@
       <c r="C41" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D41" s="72">
+      <c r="D41" s="71">
         <v>10</v>
       </c>
     </row>
@@ -2429,7 +2473,7 @@
       <c r="C52" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D52" s="72">
+      <c r="D52" s="71">
         <v>0</v>
       </c>
     </row>
@@ -2440,7 +2484,7 @@
       <c r="C53" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D53" s="72">
+      <c r="D53" s="71">
         <v>2</v>
       </c>
     </row>
@@ -2451,7 +2495,7 @@
       <c r="C54" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D54" s="72">
+      <c r="D54" s="71">
         <v>1</v>
       </c>
     </row>
@@ -2462,7 +2506,7 @@
       <c r="C55" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D55" s="72">
+      <c r="D55" s="71">
         <v>2</v>
       </c>
     </row>
@@ -2473,7 +2517,7 @@
       <c r="C56" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D56" s="72">
+      <c r="D56" s="71">
         <v>1</v>
       </c>
     </row>
@@ -2484,7 +2528,7 @@
       <c r="C57" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D57" s="72">
+      <c r="D57" s="71">
         <v>5</v>
       </c>
     </row>
@@ -2495,7 +2539,7 @@
       <c r="C58" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D58" s="72">
+      <c r="D58" s="71">
         <v>5</v>
       </c>
     </row>
@@ -2617,7 +2661,7 @@
       <c r="C68" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D68" s="72">
+      <c r="D68" s="71">
         <v>1</v>
       </c>
     </row>
@@ -2628,7 +2672,7 @@
       <c r="C69" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D69" s="73">
+      <c r="D69" s="72">
         <v>1</v>
       </c>
     </row>
@@ -2639,7 +2683,7 @@
       <c r="C70" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D70" s="72">
+      <c r="D70" s="71">
         <v>1</v>
       </c>
     </row>
@@ -2650,7 +2694,7 @@
       <c r="C71" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D71" s="72">
+      <c r="D71" s="71">
         <v>2</v>
       </c>
     </row>
@@ -2661,7 +2705,7 @@
       <c r="C72" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D72" s="72">
+      <c r="D72" s="71">
         <v>1</v>
       </c>
     </row>
@@ -2672,7 +2716,7 @@
       <c r="C73" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D73" s="72">
+      <c r="D73" s="71">
         <v>5</v>
       </c>
     </row>
@@ -2683,7 +2727,7 @@
       <c r="C74" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D74" s="72">
+      <c r="D74" s="71">
         <v>6</v>
       </c>
     </row>
@@ -2723,14 +2767,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10" style="60" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.59765625" style="60" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.296875" style="60" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" style="60" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.09765625" style="60" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="12.09765625" style="60" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="12.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="14.4" customHeight="1">
@@ -2761,38 +2805,38 @@
         <v>103</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="D2" s="74">
+        <v>106</v>
+      </c>
+      <c r="D2" s="73">
         <v>1000000</v>
       </c>
       <c r="F2" s="43" t="s">
         <v>37</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="H2" s="81"/>
-      <c r="I2" s="84" t="s">
         <v>107</v>
       </c>
-      <c r="J2" s="61" t="s">
+      <c r="H2" s="80"/>
+      <c r="I2" s="85" t="s">
         <v>108</v>
       </c>
-      <c r="K2" s="63" t="s">
+      <c r="J2" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="L2" s="62" t="s">
+      <c r="K2" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="62" t="s">
+      <c r="L2" s="61" t="s">
         <v>111</v>
       </c>
-      <c r="O2" s="64" t="s">
+      <c r="M2" s="61" t="s">
         <v>112</v>
       </c>
-      <c r="P2" s="64" t="s">
+      <c r="O2" s="63" t="s">
         <v>113</v>
+      </c>
+      <c r="P2" s="63" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="14.4" customHeight="1">
@@ -2800,27 +2844,27 @@
         <v>105</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3" s="74">
+        <v>116</v>
+      </c>
+      <c r="D3" s="73">
         <v>950000</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="G3" s="76">
+        <v>117</v>
+      </c>
+      <c r="G3" s="75">
         <v>5000000</v>
       </c>
-      <c r="H3" s="79"/>
-      <c r="I3" s="85"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="86"/>
       <c r="J3" s="46" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K3" s="47" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L3" s="48">
         <v>0</v>
@@ -2843,24 +2887,24 @@
         <v>104</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="D4" s="74">
+        <v>120</v>
+      </c>
+      <c r="D4" s="73">
         <v>900000</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="G4" s="76">
+        <v>121</v>
+      </c>
+      <c r="G4" s="75">
         <v>7000000</v>
       </c>
-      <c r="H4" s="79"/>
-      <c r="I4" s="85"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="86"/>
       <c r="J4" s="51" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K4" s="52" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="L4" s="48">
         <v>0.75</v>
@@ -2883,22 +2927,22 @@
         <v>103</v>
       </c>
       <c r="C5" s="41"/>
-      <c r="D5" s="74">
+      <c r="D5" s="73">
         <v>0</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="76">
+        <v>124</v>
+      </c>
+      <c r="G5" s="75">
         <v>2100000</v>
       </c>
-      <c r="H5" s="79"/>
-      <c r="I5" s="85"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="86"/>
       <c r="J5" s="54" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K5" s="52" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L5" s="48">
         <v>1.1000000000000001</v>
@@ -2921,30 +2965,30 @@
         <v>104</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="74">
+        <v>127</v>
+      </c>
+      <c r="D6" s="73">
         <v>900000</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>124</v>
-      </c>
-      <c r="G6" s="74">
+        <v>128</v>
+      </c>
+      <c r="G6" s="73">
         <v>2100000</v>
       </c>
-      <c r="H6" s="80"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="86"/>
       <c r="J6" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K6" s="52" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L6" s="48">
         <v>1.2</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="O6" s="57">
         <v>1.7500000000000002E-2</v>
@@ -2961,70 +3005,70 @@
         <v>103</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="D7" s="74">
+        <v>132</v>
+      </c>
+      <c r="D7" s="73">
         <v>1000000</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="G7" s="77">
+        <v>133</v>
+      </c>
+      <c r="G7" s="76">
         <v>16200000</v>
       </c>
-      <c r="H7" s="77"/>
+      <c r="H7" s="76"/>
     </row>
     <row r="8" spans="1:16" ht="26.4" customHeight="1">
       <c r="A8" s="40" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>104</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="D8" s="74">
+        <v>135</v>
+      </c>
+      <c r="D8" s="73">
         <v>1200000</v>
       </c>
-      <c r="I8" s="84" t="s">
-        <v>131</v>
-      </c>
-      <c r="J8" s="61" t="s">
-        <v>108</v>
-      </c>
-      <c r="K8" s="62" t="s">
-        <v>132</v>
-      </c>
-      <c r="L8" s="65" t="s">
-        <v>133</v>
-      </c>
-      <c r="M8" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="O8" s="63" t="s">
-        <v>135</v>
-      </c>
-      <c r="P8" s="63" t="s">
+      <c r="I8" s="85" t="s">
         <v>136</v>
+      </c>
+      <c r="J8" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="K8" s="61" t="s">
+        <v>137</v>
+      </c>
+      <c r="L8" s="64" t="s">
+        <v>138</v>
+      </c>
+      <c r="M8" s="64" t="s">
+        <v>139</v>
+      </c>
+      <c r="O8" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="P8" s="62" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="14.4" customHeight="1">
       <c r="A9" s="40" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B9" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="D9" s="74">
+        <v>142</v>
+      </c>
+      <c r="D9" s="73">
         <v>2000000</v>
       </c>
-      <c r="I9" s="85"/>
+      <c r="I9" s="86"/>
       <c r="J9" s="46" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K9" s="47">
         <v>0</v>
@@ -3044,23 +3088,23 @@
     </row>
     <row r="10" spans="1:16" ht="14.4" customHeight="1">
       <c r="A10" s="40" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B10" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="D10" s="74">
+        <v>143</v>
+      </c>
+      <c r="D10" s="73">
         <v>950000</v>
       </c>
-      <c r="I10" s="85"/>
+      <c r="I10" s="86"/>
       <c r="J10" s="51" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L10" s="48">
         <v>1.1000000000000001</v>
@@ -3077,23 +3121,23 @@
     </row>
     <row r="11" spans="1:16" ht="14.4" customHeight="1">
       <c r="A11" s="40" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B11" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="D11" s="74">
+        <v>144</v>
+      </c>
+      <c r="D11" s="73">
         <v>1000000</v>
       </c>
-      <c r="I11" s="85"/>
+      <c r="I11" s="86"/>
       <c r="J11" s="54" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="L11" s="48">
         <v>1.2</v>
@@ -3110,21 +3154,21 @@
     </row>
     <row r="12" spans="1:16" ht="14.4" customHeight="1">
       <c r="A12" s="40" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12" s="74"/>
-      <c r="I12" s="85"/>
+        <v>148</v>
+      </c>
+      <c r="D12" s="73"/>
+      <c r="I12" s="86"/>
       <c r="J12" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="L12" s="48">
         <v>1.3333333999999999</v>
@@ -3141,22 +3185,22 @@
     </row>
     <row r="13" spans="1:16" ht="14.4" customHeight="1">
       <c r="A13" s="40" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D13" s="74">
+        <v>151</v>
+      </c>
+      <c r="D13" s="73">
         <v>1000000</v>
       </c>
       <c r="J13" s="58" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="L13" s="48">
         <v>1.5</v>
@@ -3167,22 +3211,22 @@
     </row>
     <row r="14" spans="1:16" ht="14.4" customHeight="1">
       <c r="A14" s="40" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="D14" s="74">
+        <v>155</v>
+      </c>
+      <c r="D14" s="73">
         <v>2200000</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="L14" s="48">
         <v>1.6</v>
@@ -3193,15 +3237,15 @@
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" thickBot="1">
       <c r="A15" s="40" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B15" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>151</v>
-      </c>
-      <c r="D15" s="74">
+        <v>159</v>
+      </c>
+      <c r="D15" s="73">
         <v>1050000</v>
       </c>
       <c r="O15" s="45" t="s">
@@ -3213,39 +3257,39 @@
     </row>
     <row r="16" spans="1:16" ht="43.2" customHeight="1" thickBot="1">
       <c r="A16" s="40" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B16" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>152</v>
-      </c>
-      <c r="D16" s="74">
+        <v>160</v>
+      </c>
+      <c r="D16" s="73">
         <v>1050000</v>
       </c>
-      <c r="M16" s="86" t="s">
-        <v>153</v>
-      </c>
-      <c r="O16" s="63" t="s">
-        <v>154</v>
-      </c>
-      <c r="P16" s="63" t="s">
-        <v>155</v>
+      <c r="M16" s="87" t="s">
+        <v>161</v>
+      </c>
+      <c r="O16" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="P16" s="62" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="14.4" customHeight="1">
       <c r="A17" s="40" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="D17" s="74"/>
-      <c r="M17" s="87"/>
+        <v>164</v>
+      </c>
+      <c r="D17" s="73"/>
+      <c r="M17" s="88"/>
       <c r="O17" s="50">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -3255,18 +3299,18 @@
     </row>
     <row r="18" spans="1:16" ht="14.4" customHeight="1">
       <c r="A18" s="40" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B18" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="D18" s="74">
+        <v>166</v>
+      </c>
+      <c r="D18" s="73">
         <v>600000</v>
       </c>
-      <c r="M18" s="87"/>
+      <c r="M18" s="88"/>
       <c r="O18" s="53">
         <v>1.6500000000000001E-2</v>
       </c>
@@ -3276,18 +3320,18 @@
     </row>
     <row r="19" spans="1:16" ht="14.4" customHeight="1">
       <c r="A19" s="40" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B19" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="D19" s="74">
+        <v>167</v>
+      </c>
+      <c r="D19" s="73">
         <v>600000</v>
       </c>
-      <c r="M19" s="87"/>
+      <c r="M19" s="88"/>
       <c r="O19" s="55">
         <v>1.95E-2</v>
       </c>
@@ -3297,18 +3341,18 @@
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" thickBot="1">
       <c r="A20" s="40" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B20" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" s="74">
+        <v>168</v>
+      </c>
+      <c r="D20" s="73">
         <v>600000</v>
       </c>
-      <c r="M20" s="88"/>
+      <c r="M20" s="89"/>
       <c r="O20" s="57">
         <v>2.2499999999999999E-2</v>
       </c>
@@ -3318,21 +3362,21 @@
     </row>
     <row r="21" spans="1:16" ht="14.4" customHeight="1">
       <c r="A21" s="40" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="D21" s="74"/>
+        <v>170</v>
+      </c>
+      <c r="D21" s="73"/>
     </row>
     <row r="22" spans="1:16" ht="14.4" customHeight="1">
       <c r="A22" s="42"/>
       <c r="B22" s="42"/>
       <c r="C22" s="42"/>
-      <c r="D22" s="75"/>
+      <c r="D22" s="74"/>
     </row>
     <row r="23" spans="1:16" ht="14.4" customHeight="1">
       <c r="A23" s="42"/>
@@ -3341,37 +3385,37 @@
     <row r="24" spans="1:16" ht="14.4" customHeight="1">
       <c r="A24" s="42"/>
       <c r="B24" s="42"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
     </row>
     <row r="25" spans="1:16" ht="14.4" customHeight="1">
       <c r="A25" s="42"/>
       <c r="B25" s="42"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
     </row>
     <row r="26" spans="1:16" ht="14.4" customHeight="1">
       <c r="A26" s="42"/>
       <c r="B26" s="42"/>
-      <c r="F26" s="78"/>
-      <c r="G26" s="78"/>
-      <c r="H26" s="78"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
     </row>
     <row r="27" spans="1:16" ht="14.4" customHeight="1">
       <c r="A27" s="42"/>
       <c r="B27" s="42"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
     </row>
     <row r="28" spans="1:16" ht="14.4" customHeight="1">
       <c r="A28" s="42"/>
       <c r="B28" s="42"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="78"/>
-      <c r="H28" s="78"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3387,762 +3431,762 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B94"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="49.796875" style="70" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.19921875" style="70" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.8984375" style="69" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.09765625" style="69" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="66" t="s">
-        <v>161</v>
-      </c>
-      <c r="B1" s="66" t="s">
-        <v>162</v>
+      <c r="A1" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="65" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="B2" s="82" t="s">
-        <v>164</v>
+      <c r="A2" s="66" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="81" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="68" t="s">
-        <v>165</v>
-      </c>
-      <c r="B3" s="82" t="s">
+      <c r="A3" s="67" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="81" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="66" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" s="81" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="66" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="81" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="67" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="81" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="66" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="66" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="81" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="67" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="66" t="s">
+        <v>181</v>
+      </c>
+      <c r="B10" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="67" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="81" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="67" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12" s="81" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="67" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" s="81" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="66" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="66" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" s="81" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="B17" s="81" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B18" s="81" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="67" t="s">
+        <v>190</v>
+      </c>
+      <c r="B19" s="81" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="B20" s="81" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="67" t="s">
+        <v>192</v>
+      </c>
+      <c r="B21" s="81" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" s="81" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="B23" s="81" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="67" t="s">
+        <v>195</v>
+      </c>
+      <c r="B24" s="81" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="67" t="s">
+        <v>196</v>
+      </c>
+      <c r="B25" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="67" t="s">
+        <v>197</v>
+      </c>
+      <c r="B26" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="67" t="s">
+        <v>198</v>
+      </c>
+      <c r="B27" s="81" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="67" t="s">
+        <v>199</v>
+      </c>
+      <c r="B28" s="81" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="B29" s="81" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="66" t="s">
+        <v>202</v>
+      </c>
+      <c r="B30" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="67" t="s">
+        <v>203</v>
+      </c>
+      <c r="B31" s="81" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="67" t="s">
+        <v>204</v>
+      </c>
+      <c r="B32" s="81" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="66" t="s">
+        <v>205</v>
+      </c>
+      <c r="B33" s="81" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="67" t="s">
+        <v>206</v>
+      </c>
+      <c r="B34" s="81" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="67" t="s">
+    <row r="35" spans="1:2">
+      <c r="A35" s="67" t="s">
+        <v>207</v>
+      </c>
+      <c r="B35" s="81" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="67" t="s">
+        <v>208</v>
+      </c>
+      <c r="B36" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="67" t="s">
+        <v>209</v>
+      </c>
+      <c r="B37" s="81" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="67" t="s">
+        <v>210</v>
+      </c>
+      <c r="B38" s="81" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="67" t="s">
+        <v>211</v>
+      </c>
+      <c r="B39" s="81" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="67" t="s">
+        <v>212</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="67" t="s">
+        <v>213</v>
+      </c>
+      <c r="B41" s="81" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="67" t="s">
+        <v>214</v>
+      </c>
+      <c r="B42" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="67" t="s">
+        <v>215</v>
+      </c>
+      <c r="B43" s="81" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="67" t="s">
+        <v>216</v>
+      </c>
+      <c r="B44" s="81" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="66" t="s">
+        <v>217</v>
+      </c>
+      <c r="B45" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="67" t="s">
+        <v>218</v>
+      </c>
+      <c r="B46" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="67" t="s">
+        <v>219</v>
+      </c>
+      <c r="B47" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="67" t="s">
+        <v>220</v>
+      </c>
+      <c r="B48" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="67" t="s">
+        <v>221</v>
+      </c>
+      <c r="B49" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="67" t="s">
+        <v>222</v>
+      </c>
+      <c r="B50" s="81" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="82" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="67" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="82" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="68" t="s">
-        <v>170</v>
-      </c>
-      <c r="B6" s="82" t="s">
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="B51" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="67" t="s">
+        <v>224</v>
+      </c>
+      <c r="B52" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="B53" s="81" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="B54" s="81" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="67" t="s">
-        <v>171</v>
-      </c>
-      <c r="B7" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="67" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="82" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="68" t="s">
-        <v>174</v>
-      </c>
-      <c r="B9" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="67" t="s">
-        <v>175</v>
-      </c>
-      <c r="B10" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="68" t="s">
-        <v>176</v>
-      </c>
-      <c r="B11" s="82" t="s">
+    <row r="55" spans="1:2">
+      <c r="A55" s="67" t="s">
+        <v>227</v>
+      </c>
+      <c r="B55" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="67" t="s">
+        <v>228</v>
+      </c>
+      <c r="B56" s="81" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="66" t="s">
+        <v>229</v>
+      </c>
+      <c r="B57" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="67" t="s">
+        <v>230</v>
+      </c>
+      <c r="B58" s="81" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="67" t="s">
+        <v>231</v>
+      </c>
+      <c r="B59" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="67" t="s">
+        <v>232</v>
+      </c>
+      <c r="B60" s="81" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="67" t="s">
+        <v>233</v>
+      </c>
+      <c r="B61" s="81" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="67" t="s">
+        <v>234</v>
+      </c>
+      <c r="B62" s="81" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="67" t="s">
+        <v>235</v>
+      </c>
+      <c r="B63" s="81" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="67" t="s">
+        <v>236</v>
+      </c>
+      <c r="B64" s="81" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="67" t="s">
+        <v>237</v>
+      </c>
+      <c r="B65" s="81" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="67" t="s">
+        <v>238</v>
+      </c>
+      <c r="B66" s="81" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="68" t="s">
+        <v>239</v>
+      </c>
+      <c r="B67" s="81" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="68" t="s">
-        <v>177</v>
-      </c>
-      <c r="B12" s="82" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="68" t="s">
-        <v>179</v>
-      </c>
-      <c r="B13" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="68" t="s">
-        <v>180</v>
-      </c>
-      <c r="B14" s="82" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="67" t="s">
-        <v>182</v>
-      </c>
-      <c r="B15" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="67" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="82" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="68" t="s">
-        <v>184</v>
-      </c>
-      <c r="B17" s="82" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="68" t="s">
-        <v>185</v>
-      </c>
-      <c r="B18" s="82" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="68" t="s">
-        <v>186</v>
-      </c>
-      <c r="B19" s="82" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="68" t="s">
-        <v>187</v>
-      </c>
-      <c r="B20" s="82" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="68" t="s">
-        <v>189</v>
-      </c>
-      <c r="B21" s="82" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="68" t="s">
-        <v>190</v>
-      </c>
-      <c r="B22" s="82" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="68" t="s">
-        <v>191</v>
-      </c>
-      <c r="B23" s="82" t="s">
+    <row r="68" spans="1:2">
+      <c r="A68" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="B68" s="81" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="67" t="s">
+        <v>241</v>
+      </c>
+      <c r="B69" s="81" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="67" t="s">
+        <v>242</v>
+      </c>
+      <c r="B70" s="81" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="67" t="s">
+        <v>243</v>
+      </c>
+      <c r="B71" s="81" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="67" t="s">
+        <v>244</v>
+      </c>
+      <c r="B72" s="81" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="67" t="s">
+        <v>245</v>
+      </c>
+      <c r="B73" s="81" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="68" t="s">
-        <v>192</v>
-      </c>
-      <c r="B24" s="82" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="68" t="s">
-        <v>193</v>
-      </c>
-      <c r="B25" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="68" t="s">
-        <v>194</v>
-      </c>
-      <c r="B26" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="68" t="s">
-        <v>195</v>
-      </c>
-      <c r="B27" s="82" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="68" t="s">
-        <v>196</v>
-      </c>
-      <c r="B28" s="82" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="68" t="s">
-        <v>198</v>
-      </c>
-      <c r="B29" s="82" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="67" t="s">
-        <v>199</v>
-      </c>
-      <c r="B30" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="68" t="s">
-        <v>200</v>
-      </c>
-      <c r="B31" s="82" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="B32" s="82" t="s">
+    <row r="74" spans="1:2">
+      <c r="A74" s="67" t="s">
+        <v>246</v>
+      </c>
+      <c r="B74" s="81" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="67" t="s">
+        <v>247</v>
+      </c>
+      <c r="B75" s="81" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="67" t="s">
+        <v>248</v>
+      </c>
+      <c r="B76" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="67" t="s">
+        <v>249</v>
+      </c>
+      <c r="B77" s="81" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="67" t="s">
+        <v>250</v>
+      </c>
+      <c r="B78" s="81" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="67" t="s">
-        <v>202</v>
-      </c>
-      <c r="B33" s="82" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="68" t="s">
-        <v>203</v>
-      </c>
-      <c r="B34" s="82" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="68" t="s">
-        <v>205</v>
-      </c>
-      <c r="B35" s="82" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="68" t="s">
-        <v>206</v>
-      </c>
-      <c r="B36" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="68" t="s">
-        <v>207</v>
-      </c>
-      <c r="B37" s="82" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="68" t="s">
-        <v>208</v>
-      </c>
-      <c r="B38" s="82" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="68" t="s">
-        <v>209</v>
-      </c>
-      <c r="B39" s="82" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="68" t="s">
-        <v>210</v>
-      </c>
-      <c r="B40" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="68" t="s">
-        <v>211</v>
-      </c>
-      <c r="B41" s="82" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="68" t="s">
-        <v>212</v>
-      </c>
-      <c r="B42" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="68" t="s">
-        <v>213</v>
-      </c>
-      <c r="B43" s="82" t="s">
+    <row r="79" spans="1:2">
+      <c r="A79" s="67" t="s">
+        <v>251</v>
+      </c>
+      <c r="B79" s="81" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="67" t="s">
+        <v>252</v>
+      </c>
+      <c r="B80" s="81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="67" t="s">
+        <v>253</v>
+      </c>
+      <c r="B81" s="81" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="68" t="s">
-        <v>214</v>
-      </c>
-      <c r="B44" s="82" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="67" t="s">
-        <v>215</v>
-      </c>
-      <c r="B45" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="68" t="s">
-        <v>216</v>
-      </c>
-      <c r="B46" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="68" t="s">
-        <v>217</v>
-      </c>
-      <c r="B47" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="68" t="s">
-        <v>218</v>
-      </c>
-      <c r="B48" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="68" t="s">
-        <v>219</v>
-      </c>
-      <c r="B49" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="68" t="s">
-        <v>220</v>
-      </c>
-      <c r="B50" s="82" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="68" t="s">
-        <v>221</v>
-      </c>
-      <c r="B51" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="68" t="s">
-        <v>222</v>
-      </c>
-      <c r="B52" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="68" t="s">
-        <v>223</v>
-      </c>
-      <c r="B53" s="82" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="67" t="s">
-        <v>224</v>
-      </c>
-      <c r="B54" s="82" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="68" t="s">
-        <v>225</v>
-      </c>
-      <c r="B55" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="68" t="s">
-        <v>226</v>
-      </c>
-      <c r="B56" s="82" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="67" t="s">
-        <v>227</v>
-      </c>
-      <c r="B57" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="68" t="s">
-        <v>228</v>
-      </c>
-      <c r="B58" s="82" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="68" t="s">
-        <v>229</v>
-      </c>
-      <c r="B59" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="68" t="s">
-        <v>230</v>
-      </c>
-      <c r="B60" s="82" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="68" t="s">
-        <v>231</v>
-      </c>
-      <c r="B61" s="82" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="68" t="s">
-        <v>232</v>
-      </c>
-      <c r="B62" s="82" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="68" t="s">
-        <v>233</v>
-      </c>
-      <c r="B63" s="82" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="68" t="s">
-        <v>234</v>
-      </c>
-      <c r="B64" s="82" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="68" t="s">
-        <v>235</v>
-      </c>
-      <c r="B65" s="82" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="68" t="s">
-        <v>236</v>
-      </c>
-      <c r="B66" s="82" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="69" t="s">
-        <v>237</v>
-      </c>
-      <c r="B67" s="82" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="69" t="s">
-        <v>238</v>
-      </c>
-      <c r="B68" s="82" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="68" t="s">
-        <v>239</v>
-      </c>
-      <c r="B69" s="82" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="68" t="s">
-        <v>240</v>
-      </c>
-      <c r="B70" s="82" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="68" t="s">
-        <v>241</v>
-      </c>
-      <c r="B71" s="82" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="68" t="s">
-        <v>242</v>
-      </c>
-      <c r="B72" s="82" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="68" t="s">
-        <v>243</v>
-      </c>
-      <c r="B73" s="82" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="68" t="s">
-        <v>244</v>
-      </c>
-      <c r="B74" s="82" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="68" t="s">
-        <v>245</v>
-      </c>
-      <c r="B75" s="82" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="68" t="s">
-        <v>246</v>
-      </c>
-      <c r="B76" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="68" t="s">
-        <v>247</v>
-      </c>
-      <c r="B77" s="82" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="68" t="s">
-        <v>248</v>
-      </c>
-      <c r="B78" s="82" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="68" t="s">
-        <v>249</v>
-      </c>
-      <c r="B79" s="82" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="68" t="s">
-        <v>250</v>
-      </c>
-      <c r="B80" s="82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="68" t="s">
-        <v>251</v>
-      </c>
-      <c r="B81" s="82" t="s">
-        <v>204</v>
-      </c>
-    </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="69" t="s">
-        <v>252</v>
-      </c>
-      <c r="B82" s="82" t="s">
-        <v>151</v>
+      <c r="A82" s="68" t="s">
+        <v>254</v>
+      </c>
+      <c r="B82" s="81" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="68" t="s">
-        <v>253</v>
-      </c>
-      <c r="B83" s="82" t="s">
-        <v>168</v>
+      <c r="A83" s="67" t="s">
+        <v>255</v>
+      </c>
+      <c r="B83" s="81" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="B84" s="82" t="s">
-        <v>172</v>
+      <c r="A84" s="67" t="s">
+        <v>256</v>
+      </c>
+      <c r="B84" s="81" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="68" t="s">
-        <v>255</v>
-      </c>
-      <c r="B85" s="82" t="s">
-        <v>151</v>
+      <c r="A85" s="67" t="s">
+        <v>257</v>
+      </c>
+      <c r="B85" s="81" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="68" t="s">
-        <v>256</v>
-      </c>
-      <c r="B86" s="82" t="s">
-        <v>188</v>
+      <c r="A86" s="67" t="s">
+        <v>258</v>
+      </c>
+      <c r="B86" s="81" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="68" t="s">
-        <v>257</v>
-      </c>
-      <c r="B87" s="82" t="s">
-        <v>151</v>
+      <c r="A87" s="67" t="s">
+        <v>259</v>
+      </c>
+      <c r="B87" s="81" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="68" t="s">
-        <v>258</v>
-      </c>
-      <c r="B88" s="82" t="s">
-        <v>151</v>
+      <c r="A88" s="67" t="s">
+        <v>260</v>
+      </c>
+      <c r="B88" s="81" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="68" t="s">
-        <v>259</v>
-      </c>
-      <c r="B89" s="82" t="s">
-        <v>188</v>
+      <c r="A89" s="67" t="s">
+        <v>261</v>
+      </c>
+      <c r="B89" s="81" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="68" t="s">
-        <v>260</v>
-      </c>
-      <c r="B90" s="82" t="s">
-        <v>181</v>
+      <c r="A90" s="67" t="s">
+        <v>262</v>
+      </c>
+      <c r="B90" s="81" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="68" t="s">
-        <v>261</v>
-      </c>
-      <c r="B91" s="82" t="s">
-        <v>204</v>
+      <c r="A91" s="67" t="s">
+        <v>263</v>
+      </c>
+      <c r="B91" s="81" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="68" t="s">
-        <v>262</v>
-      </c>
-      <c r="B92" s="82" t="s">
-        <v>152</v>
+      <c r="A92" s="67" t="s">
+        <v>264</v>
+      </c>
+      <c r="B92" s="81" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="68" t="s">
-        <v>263</v>
-      </c>
-      <c r="B93" s="82" t="s">
-        <v>164</v>
+      <c r="A93" s="67" t="s">
+        <v>265</v>
+      </c>
+      <c r="B93" s="81" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="68" t="s">
-        <v>264</v>
-      </c>
-      <c r="B94" s="82" t="s">
-        <v>188</v>
+      <c r="A94" s="67" t="s">
+        <v>266</v>
+      </c>
+      <c r="B94" s="81" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -4155,89 +4199,89 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="30.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="14.4">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="42" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="14.4">
+      <c r="A2" s="42" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="14.4">
+      <c r="A3" s="42" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="14.4">
+      <c r="A4" s="42" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="14.4">
+      <c r="A5" s="42" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="14.4">
+      <c r="A6" s="42" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="14.4">
+      <c r="A7" s="42" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="14.4">
+      <c r="A8" s="42" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="14.4">
+      <c r="A9" s="42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="14.4">
+      <c r="A10" s="42" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="14.4">
+      <c r="A11" s="42" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="14.4">
+      <c r="A12" s="42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="14.4">
+      <c r="A13" s="42" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="14.4">
+      <c r="A14" s="42" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="14.4">
-      <c r="A2" s="83" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="14.4">
-      <c r="A3" s="83" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="14.4">
-      <c r="A4" s="83" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="14.4">
-      <c r="A5" s="83" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="14.4">
-      <c r="A6" s="83" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="14.4">
-      <c r="A7" s="83" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="14.4">
-      <c r="A8" s="83" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="14.4">
-      <c r="A9" s="83" t="s">
+    <row r="15" spans="1:1" ht="14.4">
+      <c r="A15" s="42" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="14.4">
+      <c r="A16" s="42" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="14.4">
-      <c r="A10" s="83" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="14.4">
-      <c r="A11" s="83" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="14.4">
-      <c r="A12" s="83" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="14.4">
-      <c r="A13" s="83" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="14.4">
-      <c r="A14" s="83" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="14.4">
-      <c r="A15" s="83" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="14.4">
-      <c r="A16" s="83" t="s">
-        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -4249,7 +4293,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.8984375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.296875" bestFit="1" customWidth="1"/>
@@ -4257,15 +4301,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>127</v>
       </c>
       <c r="B2">
         <v>518.58000000000004</v>
@@ -4273,7 +4317,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B3">
         <v>153.91999999999999</v>
@@ -4281,7 +4325,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>166</v>
+        <v>106</v>
       </c>
       <c r="B4">
         <v>270.5</v>
@@ -4289,7 +4333,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>116</v>
       </c>
       <c r="B5">
         <v>199.83</v>
@@ -4297,7 +4341,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B6">
         <v>7.92</v>
@@ -4305,7 +4349,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>267</v>
+        <v>120</v>
       </c>
       <c r="B7">
         <v>501.5</v>
@@ -4313,7 +4357,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B8">
         <v>57.17</v>
@@ -4321,7 +4365,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B9">
         <v>97.5</v>
@@ -4329,7 +4373,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B10">
         <v>225.67</v>
@@ -4337,7 +4381,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B11">
         <v>75.58</v>
@@ -4345,7 +4389,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B12">
         <v>74.75</v>
@@ -4353,7 +4397,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="B13">
         <v>152</v>
@@ -4361,7 +4405,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="B14">
         <v>431.67</v>
@@ -4369,7 +4413,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="B15">
         <v>935.17</v>
@@ -4378,4 +4422,721 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="28.8">
+      <c r="A1" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" s="82" t="s">
+        <v>270</v>
+      </c>
+      <c r="G1" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="I1" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q1" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="R1" s="45" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="26.4">
+      <c r="A2" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="73">
+        <v>1000000</v>
+      </c>
+      <c r="E2" s="73">
+        <v>1200000</v>
+      </c>
+      <c r="G2" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2" s="75">
+        <v>5000000</v>
+      </c>
+      <c r="I2" s="75">
+        <v>5200000</v>
+      </c>
+      <c r="K2" s="85" t="s">
+        <v>108</v>
+      </c>
+      <c r="L2" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="M2" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="N2" s="61" t="s">
+        <v>111</v>
+      </c>
+      <c r="O2" s="61" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q2" s="63" t="s">
+        <v>113</v>
+      </c>
+      <c r="R2" s="63" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="14.4">
+      <c r="A3" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="73">
+        <v>950000</v>
+      </c>
+      <c r="E3" s="73">
+        <v>1050000</v>
+      </c>
+      <c r="G3" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="H3" s="75">
+        <v>7000000</v>
+      </c>
+      <c r="I3" s="75">
+        <v>7500000</v>
+      </c>
+      <c r="K3" s="86"/>
+      <c r="L3" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="M3" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" s="48">
+        <v>0</v>
+      </c>
+      <c r="O3" s="49">
+        <v>0.74999999900000003</v>
+      </c>
+      <c r="Q3" s="50">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="R3" s="50">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="14.4">
+      <c r="A4" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="73">
+        <v>900000</v>
+      </c>
+      <c r="E4" s="73">
+        <v>950000</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="H4" s="75">
+        <v>2100000</v>
+      </c>
+      <c r="I4" s="75">
+        <v>2150000</v>
+      </c>
+      <c r="K4" s="86"/>
+      <c r="L4" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="M4" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="N4" s="48">
+        <v>0.75</v>
+      </c>
+      <c r="O4" s="49">
+        <v>1.0999999899999999</v>
+      </c>
+      <c r="Q4" s="53">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="R4" s="53">
+        <v>1.3100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="14.4">
+      <c r="A5" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="73">
+        <v>0</v>
+      </c>
+      <c r="E5" s="73">
+        <v>0</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="73">
+        <v>2100000</v>
+      </c>
+      <c r="I5" s="75">
+        <v>2150000</v>
+      </c>
+      <c r="K5" s="86"/>
+      <c r="L5" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="M5" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="N5" s="48">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="O5" s="49">
+        <v>1.1999999990000001</v>
+      </c>
+      <c r="Q5" s="55">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="R5" s="55">
+        <v>1.46E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="14.4">
+      <c r="A6" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="73">
+        <v>900000</v>
+      </c>
+      <c r="E6" s="73">
+        <v>950000</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="H6" s="84">
+        <f>SUM(H2:H5)</f>
+        <v>16200000</v>
+      </c>
+      <c r="I6" s="83">
+        <f>SUM(I2:I5)</f>
+        <v>17000000</v>
+      </c>
+      <c r="K6" s="86"/>
+      <c r="L6" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="M6" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="N6" s="48">
+        <v>1.2</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q6" s="57">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="R6" s="57">
+        <v>1.5599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="14.4">
+      <c r="A7" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="73">
+        <v>1000000</v>
+      </c>
+      <c r="E7" s="73">
+        <v>1100000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="26.4">
+      <c r="A8" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="73">
+        <v>1200000</v>
+      </c>
+      <c r="E8" s="73">
+        <v>1150000</v>
+      </c>
+      <c r="K8" s="85" t="s">
+        <v>136</v>
+      </c>
+      <c r="L8" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="M8" s="61" t="s">
+        <v>137</v>
+      </c>
+      <c r="N8" s="64" t="s">
+        <v>138</v>
+      </c>
+      <c r="O8" s="64" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q8" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="R8" s="62" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="14.4">
+      <c r="A9" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="D9" s="73">
+        <v>2000000</v>
+      </c>
+      <c r="E9" s="73">
+        <v>2000000</v>
+      </c>
+      <c r="K9" s="86"/>
+      <c r="L9" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="M9" s="47">
+        <v>0</v>
+      </c>
+      <c r="N9" s="48">
+        <v>0</v>
+      </c>
+      <c r="O9" s="49">
+        <v>1.0999999899999999</v>
+      </c>
+      <c r="Q9" s="50">
+        <v>0</v>
+      </c>
+      <c r="R9" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="14.4">
+      <c r="A10" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" s="73">
+        <v>1000000</v>
+      </c>
+      <c r="E10" s="73">
+        <v>950000</v>
+      </c>
+      <c r="K10" s="86"/>
+      <c r="L10" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="N10" s="48">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="O10" s="49">
+        <v>1.19999999</v>
+      </c>
+      <c r="Q10" s="53">
+        <v>1.5E-3</v>
+      </c>
+      <c r="R10" s="53">
+        <v>3.3999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="14.4">
+      <c r="A11" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="73">
+        <v>1000000</v>
+      </c>
+      <c r="E11" s="73">
+        <v>1150000</v>
+      </c>
+      <c r="K11" s="86"/>
+      <c r="L11" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="N11" s="48">
+        <v>1.2</v>
+      </c>
+      <c r="O11" s="49">
+        <v>1.3333333000000001</v>
+      </c>
+      <c r="Q11" s="55">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="R11" s="55">
+        <v>4.8999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="14.4">
+      <c r="A12" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" s="73">
+        <v>0</v>
+      </c>
+      <c r="E12" s="73">
+        <v>0</v>
+      </c>
+      <c r="K12" s="86"/>
+      <c r="L12" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="N12" s="48">
+        <v>1.3333333999999999</v>
+      </c>
+      <c r="O12" s="49">
+        <v>1.5</v>
+      </c>
+      <c r="Q12" s="57">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="R12" s="57">
+        <v>6.8999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="14.4">
+      <c r="A13" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="D13" s="73">
+        <v>1000000</v>
+      </c>
+      <c r="E13" s="73">
+        <v>1000000</v>
+      </c>
+      <c r="L13" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="N13" s="48">
+        <v>1.5</v>
+      </c>
+      <c r="O13" s="49">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="14.4">
+      <c r="A14" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" s="73">
+        <v>2200000</v>
+      </c>
+      <c r="E14" s="73">
+        <v>2200000</v>
+      </c>
+      <c r="L14" s="59" t="s">
+        <v>156</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="N14" s="48">
+        <v>1.6</v>
+      </c>
+      <c r="O14" s="49">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15" thickBot="1">
+      <c r="A15" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" s="73">
+        <v>1050000</v>
+      </c>
+      <c r="E15" s="73">
+        <v>1050000</v>
+      </c>
+      <c r="Q15" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="R15" s="45" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="36.6" thickBot="1">
+      <c r="A16" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" s="73">
+        <v>1050000</v>
+      </c>
+      <c r="E16" s="73">
+        <v>1050000</v>
+      </c>
+      <c r="O16" s="87" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q16" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="R16" s="62" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="14.4">
+      <c r="A17" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73">
+        <v>50000</v>
+      </c>
+      <c r="O17" s="88"/>
+      <c r="Q17" s="50">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="R17" s="50">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="14.4">
+      <c r="A18" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" s="73">
+        <v>600000</v>
+      </c>
+      <c r="E18" s="73">
+        <v>750000</v>
+      </c>
+      <c r="O18" s="88"/>
+      <c r="Q18" s="53">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="R18" s="53">
+        <v>1.6500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="14.4">
+      <c r="A19" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="D19" s="73">
+        <v>600000</v>
+      </c>
+      <c r="E19" s="73">
+        <v>750000</v>
+      </c>
+      <c r="O19" s="88"/>
+      <c r="Q19" s="55">
+        <v>1.95E-2</v>
+      </c>
+      <c r="R19" s="55">
+        <v>1.95E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="15" thickBot="1">
+      <c r="A20" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="D20" s="73">
+        <v>600000</v>
+      </c>
+      <c r="E20" s="73">
+        <v>750000</v>
+      </c>
+      <c r="O20" s="89"/>
+      <c r="Q20" s="57">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="R20" s="57">
+        <v>2.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="14.4">
+      <c r="A21" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="D21" s="73">
+        <v>0</v>
+      </c>
+      <c r="E21" s="73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="14.4">
+      <c r="A22" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B22" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="D22" s="73">
+        <v>0</v>
+      </c>
+      <c r="E22" s="73">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="K2:K6"/>
+    <mergeCell ref="K8:K12"/>
+    <mergeCell ref="O16:O20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>